--- a/data/trans_bre/IP1019-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1019-Habitat-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,6</t>
+          <t>-0,88; 1,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,33</t>
+          <t>-0,19; 0,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
